--- a/Output/pairwise_terciles_migration_lapop_stata.xlsx
+++ b/Output/pairwise_terciles_migration_lapop_stata.xlsx
@@ -13,15 +13,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="15" uniqueCount="15">
   <si>
     <t>tercile_var</t>
   </si>
   <si>
-    <t>t_interes_pol_mucho</t>
-  </si>
-  <si>
-    <t>t_en_pareja</t>
+    <t>t_density_2010</t>
+  </si>
+  <si>
+    <t>t_fem_2010</t>
+  </si>
+  <si>
+    <t>t_mean_schyr_2010</t>
+  </si>
+  <si>
+    <t>t_med_dage_2010</t>
+  </si>
+  <si>
+    <t>t_pea_2010</t>
+  </si>
+  <si>
+    <t>t_unemp_2010</t>
+  </si>
+  <si>
+    <t>t_izam_pre_avg</t>
+  </si>
+  <si>
+    <t>t_alt_pre_avg</t>
   </si>
   <si>
     <t>p_36_T1T2</t>
@@ -85,7 +103,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -93,22 +111,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2">
@@ -116,22 +134,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>0.22922410966187171</v>
+        <v>0.097743776496503607</v>
       </c>
       <c r="C2" s="1">
-        <v>0.54442918300628662</v>
+        <v>0.6499212384223938</v>
       </c>
       <c r="D2" s="1">
-        <v>0.033941797912120819</v>
+        <v>0.049375761300325394</v>
       </c>
       <c r="E2" s="1">
-        <v>0.30643133548830831</v>
+        <v>0.2226480397603797</v>
       </c>
       <c r="F2" s="1">
-        <v>0.44265332818031311</v>
+        <v>0.66384023427963257</v>
       </c>
       <c r="G2" s="1">
-        <v>0.75081592798233032</v>
+        <v>0.048534613102674484</v>
       </c>
     </row>
     <row r="3">
@@ -139,22 +157,160 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>0.74324489992616816</v>
+        <v>0.37005588546565221</v>
       </c>
       <c r="C3" s="1">
-        <v>0.1260378509759903</v>
+        <v>0.86740940809249878</v>
       </c>
       <c r="D3" s="1">
-        <v>0.028185432776808739</v>
+        <v>0.48997703194618225</v>
       </c>
       <c r="E3" s="1">
-        <v>0.57758068296622001</v>
+        <v>0.78643299039641568</v>
       </c>
       <c r="F3" s="1">
-        <v>0.14435315132141113</v>
+        <v>0.64150995016098022</v>
       </c>
       <c r="G3" s="1">
-        <v>0.2777717113494873</v>
+        <v>0.56055659055709839</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.0015731090000392</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.034954790025949478</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.29983726143836975</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0.0134828595512948</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0.2802223265171051</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.042192887514829636</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>0.1687903748729139</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.56747454404830933</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.054058860987424851</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0.13753964158160301</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.46116143465042114</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.32734459638595581</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>0.47426135205524389</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.13625916838645935</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.88028842210769653</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.63913181924770335</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.49932140111923218</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.51390373706817627</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0.97024372937514669</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.87026596069335938</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.71472769975662232</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.75517941648736875</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.85956704616546631</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.52846384048461914</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0.97811693905385622</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.92974787950515747</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.87120962142944336</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.5813446668917911</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.8302457332611084</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.66686803102493286</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.71652613079387362</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.98823195695877075</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.79876714944839478</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.97801077949383475</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.66347628831863403</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0.67566275596618652</v>
       </c>
     </row>
   </sheetData>
